--- a/data/trans_dic/DCD-Edad-trans_dic.xlsx
+++ b/data/trans_dic/DCD-Edad-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dolor crónico discapacitante</t>
+          <t>Población con dolor crónico discapacitante (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,43; 2,65</t>
+          <t>0,44; 2,69</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,66</t>
+          <t>0,0; 1,46</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,49; 5,07</t>
+          <t>0,5; 4,88</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,97; 7,33</t>
+          <t>2,99; 7,15</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,99; 5,53</t>
+          <t>1,97; 5,4</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,42; 23,2</t>
+          <t>11,22; 23,15</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,94; 4,41</t>
+          <t>1,95; 4,27</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,17; 3,01</t>
+          <t>1,1; 2,93</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,38; 11,17</t>
+          <t>5,79; 11,56</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,59; 4,21</t>
+          <t>1,73; 4,22</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,72; 4,93</t>
+          <t>1,69; 4,92</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,83; 7,93</t>
+          <t>2,91; 8,03</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,97; 8,94</t>
+          <t>4,91; 9,25</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,72; 9,0</t>
+          <t>4,67; 8,81</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,46; 16,51</t>
+          <t>7,56; 16,49</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,53; 5,99</t>
+          <t>3,42; 5,93</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,51; 6,09</t>
+          <t>3,6; 6,08</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,34; 11,39</t>
+          <t>6,7; 11,46</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,86; 6,07</t>
+          <t>2,93; 6,05</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,55; 5,78</t>
+          <t>2,57; 5,73</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,5; 10,51</t>
+          <t>5,51; 10,42</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9,52; 14,61</t>
+          <t>9,56; 14,6</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,85; 11,35</t>
+          <t>6,68; 11,27</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12,15; 18,96</t>
+          <t>11,99; 19,0</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,65; 9,65</t>
+          <t>6,51; 9,75</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,08; 7,82</t>
+          <t>5,03; 7,8</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>9,87; 13,88</t>
+          <t>10,0; 14,09</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,61; 8,74</t>
+          <t>4,71; 9,21</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,66; 8,76</t>
+          <t>4,68; 8,75</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,31; 14,84</t>
+          <t>4,47; 15,09</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11,72; 17,64</t>
+          <t>11,59; 17,63</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>10,33; 15,96</t>
+          <t>10,53; 15,93</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,96; 26,64</t>
+          <t>20,12; 26,77</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,96; 12,43</t>
+          <t>8,83; 12,55</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8,06; 11,55</t>
+          <t>8,06; 11,47</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>9,34; 19,71</t>
+          <t>10,3; 20,03</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>6,22; 11,71</t>
+          <t>6,22; 11,81</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>9,45; 15,73</t>
+          <t>9,4; 15,47</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16,98; 23,34</t>
+          <t>17,24; 23,69</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17,71; 25,78</t>
+          <t>17,3; 25,78</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>14,52; 21,44</t>
+          <t>14,53; 21,69</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>28,72; 34,58</t>
+          <t>28,65; 34,45</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,93; 17,84</t>
+          <t>12,77; 17,7</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>12,81; 17,68</t>
+          <t>12,71; 17,85</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>23,69; 28,09</t>
+          <t>23,73; 28,14</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>10,97; 19,42</t>
+          <t>11,03; 19,75</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6,66; 13,59</t>
+          <t>6,72; 13,37</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>15,15; 21,33</t>
+          <t>15,34; 21,89</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>23,52; 32,95</t>
+          <t>23,97; 33,3</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>13,54; 21,43</t>
+          <t>13,87; 21,76</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>8,99; 33,82</t>
+          <t>9,8; 34,32</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>19,05; 25,42</t>
+          <t>18,92; 25,38</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>11,17; 16,33</t>
+          <t>11,42; 16,67</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>11,45; 26,95</t>
+          <t>11,12; 26,79</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>15,42; 25,79</t>
+          <t>15,37; 26,3</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>15,49; 24,8</t>
+          <t>15,22; 24,6</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>26,13; 34,32</t>
+          <t>25,78; 34,15</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>33,28; 43,5</t>
+          <t>33,44; 43,69</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>24,24; 34,12</t>
+          <t>24,05; 33,79</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>47,04; 53,94</t>
+          <t>46,76; 54,44</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>27,62; 35,14</t>
+          <t>27,75; 35,54</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>21,79; 29,29</t>
+          <t>21,53; 28,91</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>39,55; 45,15</t>
+          <t>39,5; 44,9</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>5,82; 7,6</t>
+          <t>5,79; 7,5</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>5,87; 7,69</t>
+          <t>5,87; 7,64</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9,76; 13,79</t>
+          <t>9,71; 13,78</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>15,09; 17,6</t>
+          <t>15,1; 17,56</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>11,91; 14,25</t>
+          <t>12,0; 14,39</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>19,84; 26,3</t>
+          <t>19,47; 26,27</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,85; 12,33</t>
+          <t>10,78; 12,35</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>9,21; 10,71</t>
+          <t>9,2; 10,68</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>16,09; 19,92</t>
+          <t>15,87; 19,86</t>
         </is>
       </c>
     </row>
@@ -1543,7 +1543,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dolor crónico discapacitante</t>
+          <t>Población con dolor crónico discapacitante (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1750,47 +1750,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1955; 12051</t>
+          <t>2014; 12204</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 6980</t>
+          <t>0; 6141</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1979; 20263</t>
+          <t>1992; 19500</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12781; 31550</t>
+          <t>12848; 30740</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>7882; 21884</t>
+          <t>7789; 21371</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>35761; 72660</t>
+          <t>35152; 72502</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>17192; 38990</t>
+          <t>17264; 37785</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>9521; 24526</t>
+          <t>8932; 23896</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>38377; 79656</t>
+          <t>41304; 82452</t>
         </is>
       </c>
     </row>
@@ -1913,47 +1913,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10956; 28911</t>
+          <t>11864; 28990</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10186; 29106</t>
+          <t>9987; 29046</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11982; 33571</t>
+          <t>12318; 34005</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>30337; 54533</t>
+          <t>29981; 56438</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>26618; 50696</t>
+          <t>26311; 49671</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>38177; 84558</t>
+          <t>38721; 84447</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>45749; 77661</t>
+          <t>44311; 76925</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>40487; 70285</t>
+          <t>41548; 70153</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>59285; 106588</t>
+          <t>62676; 107221</t>
         </is>
       </c>
     </row>
@@ -2076,47 +2076,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>19500; 41413</t>
+          <t>19952; 41285</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>17053; 38671</t>
+          <t>17190; 38316</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>29485; 56384</t>
+          <t>29546; 55897</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>67701; 103828</t>
+          <t>67988; 103761</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>45278; 75036</t>
+          <t>44158; 74563</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>71923; 112253</t>
+          <t>70956; 112457</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>92680; 134375</t>
+          <t>90637; 135753</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>67589; 104020</t>
+          <t>66875; 103731</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>111341; 156669</t>
+          <t>112821; 159019</t>
         </is>
       </c>
     </row>
@@ -2239,47 +2239,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>28344; 53716</t>
+          <t>28920; 56607</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>30116; 56605</t>
+          <t>30205; 56508</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>38280; 131716</t>
+          <t>39716; 134003</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>72193; 108720</t>
+          <t>71409; 108648</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>67071; 103606</t>
+          <t>68342; 103393</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>142292; 189891</t>
+          <t>143432; 190872</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>110256; 152943</t>
+          <t>108656; 154445</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>104427; 149573</t>
+          <t>104433; 148581</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>149432; 315420</t>
+          <t>164923; 320612</t>
         </is>
       </c>
     </row>
@@ -2402,47 +2402,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>26690; 50266</t>
+          <t>26707; 50722</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>45178; 75182</t>
+          <t>44918; 73917</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>95276; 131000</t>
+          <t>96738; 132931</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>79314; 115430</t>
+          <t>77456; 115464</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>72166; 106535</t>
+          <t>72197; 107769</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>157359; 189460</t>
+          <t>156958; 188757</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>113460; 156457</t>
+          <t>112064; 155261</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>124854; 172342</t>
+          <t>123858; 173958</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>262789; 311526</t>
+          <t>263175; 312063</t>
         </is>
       </c>
     </row>
@@ -2565,47 +2565,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>33983; 60168</t>
+          <t>34157; 61184</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>22255; 45449</t>
+          <t>22452; 44701</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>55760; 78539</t>
+          <t>56484; 80576</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>83271; 116648</t>
+          <t>84849; 117876</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>51157; 80940</t>
+          <t>52399; 82209</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>54699; 205753</t>
+          <t>59646; 208779</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>126473; 168729</t>
+          <t>125601; 168458</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>79566; 116300</t>
+          <t>81297; 118713</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>111828; 263128</t>
+          <t>108560; 261653</t>
         </is>
       </c>
     </row>
@@ -2728,47 +2728,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>38533; 64444</t>
+          <t>38405; 65709</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>39808; 63738</t>
+          <t>39108; 63219</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>73877; 97054</t>
+          <t>72900; 96556</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>129461; 169192</t>
+          <t>130083; 169948</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>96999; 136531</t>
+          <t>96252; 135226</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>200327; 229710</t>
+          <t>199127; 231801</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>176448; 224476</t>
+          <t>177260; 227037</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>143215; 192496</t>
+          <t>141507; 190005</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>280262; 319947</t>
+          <t>279868; 318129</t>
         </is>
       </c>
     </row>
@@ -2891,47 +2891,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>199449; 260328</t>
+          <t>198343; 256990</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>199191; 260919</t>
+          <t>199386; 259359</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>337616; 477084</t>
+          <t>336018; 476740</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>537033; 626371</t>
+          <t>537418; 624984</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>422039; 505227</t>
+          <t>425440; 510224</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>736624; 976182</t>
+          <t>722617; 975036</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>757863; 861259</t>
+          <t>753113; 862980</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>639330; 743382</t>
+          <t>638683; 741169</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1154101; 1428993</t>
+          <t>1138230; 1424504</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/DCD-Edad-trans_dic.xlsx
+++ b/data/trans_dic/DCD-Edad-trans_dic.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,8%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,44; 2,69</t>
+          <t>0,43; 2,77</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,46</t>
+          <t>0,0; 1,65</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,5; 4,88</t>
+          <t>0,0; 4,69</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,99; 7,15</t>
+          <t>3,0; 7,24</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,97; 5,4</t>
+          <t>2,15; 5,39</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,22; 23,15</t>
+          <t>11,7; 22,83</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,95; 4,27</t>
+          <t>2,03; 4,28</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,1; 2,93</t>
+          <t>1,1; 3,04</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,79; 11,56</t>
+          <t>6,19; 12,36</t>
         </is>
       </c>
     </row>
@@ -745,37 +745,37 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
+          <t>4,97%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>6,76%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>6,62%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>13,79%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>4,62%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>4,78%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>6,76%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>6,62%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>12,54%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>4,62%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>4,78%</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,49%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,73; 4,22</t>
+          <t>1,73; 4,39</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,69; 4,92</t>
+          <t>1,73; 4,9</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,91; 8,03</t>
+          <t>2,8; 8,02</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,91; 9,25</t>
+          <t>4,91; 9,18</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,67; 8,81</t>
+          <t>4,8; 9,18</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,56; 16,49</t>
+          <t>10,56; 17,18</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,42; 5,93</t>
+          <t>3,49; 5,87</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,6; 6,08</t>
+          <t>3,58; 6,08</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,7; 11,46</t>
+          <t>7,47; 11,67</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>12,37%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,93; 6,05</t>
+          <t>2,84; 6,31</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,57; 5,73</t>
+          <t>2,48; 5,67</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,51; 10,42</t>
+          <t>4,95; 9,28</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9,56; 14,6</t>
+          <t>9,27; 14,49</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,68; 11,27</t>
+          <t>6,9; 11,46</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11,99; 19,0</t>
+          <t>15,38; 20,87</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,51; 9,75</t>
+          <t>6,7; 9,65</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,03; 7,8</t>
+          <t>5,19; 7,74</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>10,0; 14,09</t>
+          <t>10,75; 14,26</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>24,66%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>19,26%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,71; 9,21</t>
+          <t>4,7; 8,84</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,68; 8,75</t>
+          <t>4,71; 8,53</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,47; 15,09</t>
+          <t>11,15; 16,43</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11,59; 17,63</t>
+          <t>11,76; 17,83</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>10,53; 15,93</t>
+          <t>10,52; 15,77</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>20,12; 26,77</t>
+          <t>22,23; 27,38</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,83; 12,55</t>
+          <t>8,89; 12,4</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8,06; 11,47</t>
+          <t>8,11; 11,47</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>10,3; 20,03</t>
+          <t>17,48; 21,19</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>31,46%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>25,91%</t>
+          <t>25,49%</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>6,22; 11,81</t>
+          <t>6,23; 11,4</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>9,4; 15,47</t>
+          <t>9,15; 15,81</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17,24; 23,69</t>
+          <t>16,66; 22,76</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17,3; 25,78</t>
+          <t>17,6; 25,37</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>14,53; 21,69</t>
+          <t>14,71; 21,94</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>28,65; 34,45</t>
+          <t>28,6; 34,31</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,77; 17,7</t>
+          <t>12,96; 17,86</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>12,71; 17,85</t>
+          <t>12,87; 17,7</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>23,73; 28,14</t>
+          <t>23,29; 27,92</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1185,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>33,53%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>26,02%</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>11,03; 19,75</t>
+          <t>11,17; 19,54</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6,72; 13,37</t>
+          <t>6,61; 13,41</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>15,34; 21,89</t>
+          <t>14,64; 21,26</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>23,97; 33,3</t>
+          <t>23,43; 33,01</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>13,87; 21,76</t>
+          <t>13,87; 21,6</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9,8; 34,32</t>
+          <t>30,29; 36,93</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>18,92; 25,38</t>
+          <t>18,88; 25,52</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>11,42; 16,67</t>
+          <t>11,36; 16,41</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>11,12; 26,79</t>
+          <t>23,81; 28,68</t>
         </is>
       </c>
     </row>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>29,99%</t>
+          <t>30,28%</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>50,46%</t>
+          <t>50,97%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>42,29%</t>
+          <t>42,68%</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>15,37; 26,3</t>
+          <t>15,08; 25,47</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>15,22; 24,6</t>
+          <t>15,13; 24,51</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>25,78; 34,15</t>
+          <t>25,79; 34,83</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>33,44; 43,69</t>
+          <t>33,23; 43,75</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>24,05; 33,79</t>
+          <t>23,69; 33,62</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>46,76; 54,44</t>
+          <t>47,28; 54,11</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>27,75; 35,54</t>
+          <t>27,62; 35,22</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>21,53; 28,91</t>
+          <t>21,79; 29,01</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>39,5; 44,9</t>
+          <t>39,87; 45,18</t>
         </is>
       </c>
     </row>
@@ -1405,7 +1405,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>19,98%</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>5,79; 7,5</t>
+          <t>5,78; 7,5</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>5,87; 7,64</t>
+          <t>5,94; 7,63</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9,71; 13,78</t>
+          <t>11,84; 14,24</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>15,1; 17,56</t>
+          <t>15,09; 17,61</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>12,0; 14,39</t>
+          <t>11,92; 14,22</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>19,47; 26,27</t>
+          <t>25,49; 28,05</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,78; 12,35</t>
+          <t>10,85; 12,47</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>9,2; 10,68</t>
+          <t>9,25; 10,71</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>15,87; 19,86</t>
+          <t>19,06; 20,87</t>
         </is>
       </c>
     </row>
@@ -1707,7 +1707,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7206</t>
+          <t>6928</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1722,7 +1722,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>50324</t>
+          <t>60871</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1737,7 +1737,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>57531</t>
+          <t>67799</t>
         </is>
       </c>
     </row>
@@ -1750,47 +1750,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2014; 12204</t>
+          <t>1951; 12580</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 6141</t>
+          <t>0; 6919</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1992; 19500</t>
+          <t>0; 19113</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12848; 30740</t>
+          <t>12909; 31144</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>7789; 21371</t>
+          <t>8490; 21324</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>35152; 72502</t>
+          <t>42431; 82765</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>17264; 37785</t>
+          <t>17950; 37812</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>8932; 23896</t>
+          <t>8976; 24762</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>41304; 82452</t>
+          <t>47688; 95229</t>
         </is>
       </c>
     </row>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>20237</t>
+          <t>23681</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1885,7 +1885,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>64231</t>
+          <t>69185</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>84468</t>
+          <t>92866</t>
         </is>
       </c>
     </row>
@@ -1913,47 +1913,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>11864; 28990</t>
+          <t>11882; 30166</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9987; 29046</t>
+          <t>10221; 28939</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12318; 34005</t>
+          <t>13369; 38270</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>29981; 56438</t>
+          <t>29978; 56042</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>26311; 49671</t>
+          <t>27059; 51759</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>38721; 84447</t>
+          <t>52963; 86179</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>44311; 76925</t>
+          <t>45327; 76137</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>41548; 70153</t>
+          <t>41326; 70178</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>62676; 107221</t>
+          <t>73080; 114214</t>
         </is>
       </c>
     </row>
@@ -2033,7 +2033,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>41234</t>
+          <t>43275</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94645</t>
+          <t>110551</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>135879</t>
+          <t>153827</t>
         </is>
       </c>
     </row>
@@ -2076,47 +2076,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>19952; 41285</t>
+          <t>19378; 43022</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>17190; 38316</t>
+          <t>16567; 37951</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>29546; 55897</t>
+          <t>30722; 57588</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>67988; 103761</t>
+          <t>65888; 102992</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>44158; 74563</t>
+          <t>45631; 75786</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>70956; 112457</t>
+          <t>95867; 130039</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>90637; 135753</t>
+          <t>93288; 134393</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>66875; 103731</t>
+          <t>69025; 102976</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>112821; 159019</t>
+          <t>133736; 177369</t>
         </is>
       </c>
     </row>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>89870</t>
+          <t>95227</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>168927</t>
+          <t>181708</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>258797</t>
+          <t>276935</t>
         </is>
       </c>
     </row>
@@ -2239,47 +2239,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>28920; 56607</t>
+          <t>28887; 54332</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>30205; 56508</t>
+          <t>30433; 55087</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>39716; 134003</t>
+          <t>78092; 115100</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>71409; 108648</t>
+          <t>72443; 109862</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>68342; 103393</t>
+          <t>68256; 102364</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>143432; 190872</t>
+          <t>163807; 201724</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>108656; 154445</t>
+          <t>109381; 152594</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>104433; 148581</t>
+          <t>105027; 148496</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>164923; 320612</t>
+          <t>251219; 304641</t>
         </is>
       </c>
     </row>
@@ -2359,7 +2359,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>113477</t>
+          <t>118949</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>173924</t>
+          <t>191528</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2389,7 +2389,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>287401</t>
+          <t>310477</t>
         </is>
       </c>
     </row>
@@ -2402,47 +2402,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>26707; 50722</t>
+          <t>26770; 48971</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>44918; 73917</t>
+          <t>43739; 75581</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>96738; 132931</t>
+          <t>101537; 138663</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>77456; 115464</t>
+          <t>78833; 113587</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>72197; 107769</t>
+          <t>73073; 108997</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>156958; 188757</t>
+          <t>174161; 208907</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>112064; 155261</t>
+          <t>113707; 156655</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>123858; 173958</t>
+          <t>125416; 172490</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>263175; 312063</t>
+          <t>283693; 340158</t>
         </is>
       </c>
     </row>
@@ -2522,7 +2522,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>67209</t>
+          <t>72921</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>133024</t>
+          <t>147273</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2552,7 +2552,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>200234</t>
+          <t>220194</t>
         </is>
       </c>
     </row>
@@ -2565,47 +2565,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>34157; 61184</t>
+          <t>34615; 60540</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>22452; 44701</t>
+          <t>22085; 44831</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>56484; 80576</t>
+          <t>59586; 86532</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>84849; 117876</t>
+          <t>82926; 116857</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>52399; 82209</t>
+          <t>52404; 81589</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>59646; 208779</t>
+          <t>133015; 162173</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>125601; 168458</t>
+          <t>125312; 169414</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>81297; 118713</t>
+          <t>80889; 116850</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>108560; 261653</t>
+          <t>201515; 242666</t>
         </is>
       </c>
     </row>
@@ -2685,7 +2685,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>84812</t>
+          <t>93930</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2700,7 +2700,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>214876</t>
+          <t>236792</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>299688</t>
+          <t>330722</t>
         </is>
       </c>
     </row>
@@ -2728,47 +2728,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>38405; 65709</t>
+          <t>37689; 63634</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>39108; 63219</t>
+          <t>38892; 62999</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>72900; 96556</t>
+          <t>80005; 108028</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>130083; 169948</t>
+          <t>129271; 170184</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>96252; 135226</t>
+          <t>94789; 134548</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>199127; 231801</t>
+          <t>219655; 251396</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>177260; 227037</t>
+          <t>176456; 224986</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>141507; 190005</t>
+          <t>143171; 190659</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>279868; 318129</t>
+          <t>308924; 350074</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>424045</t>
+          <t>454911</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -2863,7 +2863,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>899952</t>
+          <t>997910</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>1323997</t>
+          <t>1452821</t>
         </is>
       </c>
     </row>
@@ -2891,47 +2891,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>198343; 256990</t>
+          <t>198146; 256925</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>199386; 259359</t>
+          <t>201723; 258952</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>336018; 476740</t>
+          <t>418162; 503157</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>537418; 624984</t>
+          <t>536814; 626754</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>425440; 510224</t>
+          <t>422673; 503963</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>722617; 975036</t>
+          <t>952398; 1048222</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>753113; 862980</t>
+          <t>757979; 871047</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>638683; 741169</t>
+          <t>642058; 743100</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1138230; 1424504</t>
+          <t>1385950; 1517258</t>
         </is>
       </c>
     </row>
